--- a/college-posters/data/字段表_211第五批.xlsx
+++ b/college-posters/data/字段表_211第五批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>农业与生物、党政机关与事业单位、贵州本地企业</t>
+          <t>花溪校区：山水环绕的主校区；花溪河：流经校园的河流；图书馆：花溪校区标志建筑</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>贵州大学</t>
+          <t>广西大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>花溪校区：山水环绕的主校区；花溪河：流经校园的河流；图书馆：花溪校区标志建筑</t>
+          <t>土木工程、轻化工程、农学、电气工程及其自动化、计算机科学与技术、法学</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>贵州大学</t>
+          <t>广西大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>西校园：南宁主校区；东校园：原广西农大校区；君武馆：纪念马君武校长</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>广西大学</t>
+          <t>海南大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>土木工程、轻化工程、农学、电气工程及其自动化、计算机科学与技术、法学</t>
+          <t>农学、园艺、海洋科学、旅游管理、法学、计算机科学与技术</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>广西大学</t>
+          <t>海南大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>建筑与土木工程、糖业与农业、面向东盟的外贸企业</t>
+          <t>海甸校区：海口海甸岛临海校区；城西校区：海口城西校区；儋州校区：热带农业校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>广西大学</t>
+          <t>长安大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>西校园：南宁主校区；东校园：原广西农大校区；君武馆：纪念马君武校长</t>
+          <t>交通工程、土木工程、道路桥梁与渡河工程、车辆工程、地质工程、测绘工程</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>广西大学</t>
+          <t>长安大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>本部校区：西安南二环校区；渭水校区：西咸新区校区；试验场：汽车与道路试验场</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>海南大学</t>
+          <t>湖南师范大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>农学、园艺、海洋科学、旅游管理、法学、计算机科学与技术</t>
+          <t>英语、汉语言文学、教育学、心理学、数学与应用数学、新闻学</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,117 +676,117 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>海南大学</t>
+          <t>湖南师范大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>热带农业与科研、旅游与服务业、海南自贸港企业</t>
+          <t>二里半校区：岳麓山下主校区；桃花坪校区：长沙校区；湘江：校园毗邻湘江</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>海南大学</t>
+          <t>太原理工大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>海甸校区：海口海甸岛临海校区；城西校区：海口城西校区；儋州校区：热带农业校区</t>
+          <t>化学工程与工艺、采矿工程、材料科学与工程、机械工程、电气工程及其自动化、计算机科学与技术</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>海南大学</t>
+          <t>太原理工大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>迎西校区：太原主校区；明向校区：晋中大学城校区；虎峪校区：太原校区</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>长安大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>交通工程、土木工程、道路桥梁与渡河工程、车辆工程、地质工程、测绘工程</t>
+          <t>2026年第101名（较上年下降）</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>长安大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>交通建设与路桥、地质勘察与测绘、汽车与工程机械</t>
+          <t>材料科学与工程、电子信息工程、计算机科学与技术、法学、汉语言文学、经济学</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>长安大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>本部校区：西安南二环校区；渭水校区：西咸新区校区；试验场：汽车与道路试验场</t>
+          <t>磬苑校区：合肥主校区；龙河校区：老校区；文典阁：以刘文典命名的图书馆</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -808,29 +808,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>长安大学</t>
+          <t>河北工业大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>2026年第107名</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（单一第三方来源）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>湖南师范大学</t>
+          <t>河北工业大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>英语、汉语言文学、教育学、心理学、数学与应用数学、新闻学</t>
+          <t>电气工程及其自动化、材料科学与工程、化学工程与工艺、机械设计制造及其自动化、计算机科学与技术、土木工程</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -852,638 +852,110 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>湖南师范大学</t>
+          <t>河北工业大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒</t>
+          <t>北辰校区：天津主校区；红桥校区：老校区；廊坊校区：河北廊坊校区</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>湖南师范大学</t>
+          <t>大连海事大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>二里半校区：岳麓山下主校区；桃花坪校区：长沙校区；湘江：校园毗邻湘江</t>
+          <t>航海技术、轮机工程、交通运输、船舶电子电气工程、海事管理、法学</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>湖南师范大学</t>
+          <t>大连海事大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>凌海路校区：黄海之滨的校园；码头：教学实习船停靠处；主楼：校园标志建筑</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>太原理工大学</t>
+          <t>内蒙古大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>软科中国大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026年第97名</t>
+          <t>生物科学、蒙古语言文学、生态学、化学、计算机科学与技术、法学</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核（单一第三方来源）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>太原理工大学</t>
+          <t>内蒙古大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>化学工程与工艺、采矿工程、材料科学与工程、机械工程、电气工程及其自动化、计算机科学与技术</t>
+          <t>南校区：呼和浩特主校区；北校区：老校区；南寨校区：新建校区</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>太原理工大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>煤炭与能源、化工与材料、山西本地企业</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>太原理工大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>迎西校区：太原主校区；明向校区：晋中大学城校区；虎峪校区：太原校区</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>太原理工大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>软科中国大学排名</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026年第101名（较上年下降）</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核（单一来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>材料科学与工程、电子信息工程、计算机科学与技术、法学、汉语言文学、经济学</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与制造、党政机关与事业单位、长三角企业</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>磬苑校区：合肥主校区；龙河校区：老校区；文典阁：以刘文典命名的图书馆</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>软科中国大学排名</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2026年第107名</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核（单一第三方来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>双一流1个：电气工程（转载名单未见具体学科名，按记忆填写）；办学123年</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>双一流建设学科</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>电气工程</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>电气工程及其自动化、材料科学与工程、化学工程与工艺、机械设计制造及其自动化、计算机科学与技术、土木工程</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>电气与能源、先进制造、京津冀企业</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>北辰校区：天津主校区；红桥校区：老校区；廊坊校区：河北廊坊校区</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>河北工业大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>大连海事大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>航海技术、轮机工程、交通运输、船舶电子电气工程、海事管理、法学</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>大连海事大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>航运与港口、船舶与海事、交通运输与物流</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>大连海事大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>凌海路校区：黄海之滨的校园；码头：教学实习船停靠处；主楼：校园标志建筑</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>大连海事大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学校训原文未核到，海报竖排改放运营寄语“扎根北疆”，印章写“寄语”而非“校训”</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>生物科学、蒙古语言文学、生态学、化学、计算机科学与技术、法学</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>党政机关与事业单位、生物与生态、内蒙古本地企业</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>南校区：呼和浩特主校区；北校区：老校区；南寨校区：新建校区</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古大学</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -2047,9 +1519,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2172,12 +1644,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2408,22 +1880,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>内蒙古大学校训原文未核到，海报竖排改放运营寄语“扎根北疆”，印章写“寄语”而非“校训”</t>
+          <t>求真务实（内蒙古自治区教育厅核准的章程修正案）；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>扎根 北疆</t>
+          <t>求真 务实</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
+          <t>内蒙古教育厅文件</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -2805,9 +2277,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2402,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3563,9 +3035,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3160,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4321,9 +3793,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4446,12 +3918,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5079,9 +4551,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5204,12 +4676,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5837,9 +5309,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6595,9 +6067,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6720,12 +6192,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7030,12 +6502,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>高考100 · 211排名表</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>待核（单一第三方来源）</t>
+          <t>xuanxiao.org、网易转载（两源一致）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致）</t>
         </is>
       </c>
     </row>
@@ -7353,9 +6825,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7478,12 +6950,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8111,9 +7583,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8236,12 +7708,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8104,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>双一流1个：电气工程（转载名单未见具体学科名，按记忆填写）；办学123年</t>
+          <t>双一流1个：电气工程</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8645,9 +8117,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8709,9 +8181,9 @@
           <t>教育部 第二轮双一流名单（转载）</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8869,9 +8341,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8466,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
